--- a/empresas_backup.xlsx
+++ b/empresas_backup.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tiago\OneDrive\Documentos\Python\onstage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAEA17E7-2E35-4406-9FA9-DA3507FE08C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{738A57FA-B265-40D2-ACD1-E747E6317E17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5940" yWindow="420" windowWidth="20460" windowHeight="10770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="247">
   <si>
     <t>Nome empresa</t>
   </si>
@@ -34,13 +34,733 @@
     <t>nsu</t>
   </si>
   <si>
-    <t>MEDF Serviços Médicos</t>
+    <t>1 - I M PRESTAÇÃO DE SERVIÇOS MÉDICOS LTDA</t>
+  </si>
+  <si>
+    <t>49145678000151</t>
+  </si>
+  <si>
+    <t>Im49145@2026</t>
+  </si>
+  <si>
+    <t>2 - I.A.C.G. PRESTAÇÃO DE SERVIÇOS MÉDICOS LTDA</t>
+  </si>
+  <si>
+    <t>49456081000128</t>
+  </si>
+  <si>
+    <t>3 - MEDF SERVIÇOS MÉDICOS LTDA</t>
   </si>
   <si>
     <t>49899508000162</t>
   </si>
   <si>
-    <t>Medf@2025</t>
+    <t>Me49899@2026</t>
+  </si>
+  <si>
+    <t>5 - CENTRO TERAPÊUTICO T&amp;T LTDA</t>
+  </si>
+  <si>
+    <t>50219602000102</t>
+  </si>
+  <si>
+    <t>Ded50219@2026</t>
+  </si>
+  <si>
+    <t>7 - GASTROMED SERVIÇOS MÉDICOS LTDA.</t>
+  </si>
+  <si>
+    <t>51223925000132</t>
+  </si>
+  <si>
+    <t>Gastro@2025</t>
+  </si>
+  <si>
+    <t>10 - MELISSA XAVIER MENEZES</t>
+  </si>
+  <si>
+    <t>43092673000121</t>
+  </si>
+  <si>
+    <t>Melissa@2025</t>
+  </si>
+  <si>
+    <t>11 - PABLO FERNANDES DUARTE MACHADO</t>
+  </si>
+  <si>
+    <t>41933439000154</t>
+  </si>
+  <si>
+    <t>Pa41933@2025</t>
+  </si>
+  <si>
+    <t>14 - JM SERVIÇOS MÉDICOS LTDA.</t>
+  </si>
+  <si>
+    <t>53206430000120</t>
+  </si>
+  <si>
+    <t>Jm53206@2026</t>
+  </si>
+  <si>
+    <t>15 - R. ENERGY REPRESENTAÇÕES LTDA.</t>
+  </si>
+  <si>
+    <t>53967864000143</t>
+  </si>
+  <si>
+    <t>Re53967@2026</t>
+  </si>
+  <si>
+    <t>16 - LC SERVICOS DE SAUDE LTDA.</t>
+  </si>
+  <si>
+    <t>54604353000120</t>
+  </si>
+  <si>
+    <t>Lc54604@2026</t>
+  </si>
+  <si>
+    <t>18 - RRS SAUDE LTDA.</t>
+  </si>
+  <si>
+    <t>54650100000192</t>
+  </si>
+  <si>
+    <t>Rr54650@2026</t>
+  </si>
+  <si>
+    <t>20 - D.A SERVICOS MEDICOS LTDA.</t>
+  </si>
+  <si>
+    <t>54846807000179</t>
+  </si>
+  <si>
+    <t>Da54846@2026</t>
+  </si>
+  <si>
+    <t>21 - SOARES E LOBO SERVICOS MEDICOS LTDA</t>
+  </si>
+  <si>
+    <t>38826274000107</t>
+  </si>
+  <si>
+    <t>Yasmin@2025</t>
+  </si>
+  <si>
+    <t>25 - PSIQUE SERVICOS DE PSICOLOGIA E MEDICINA LTDA</t>
+  </si>
+  <si>
+    <t>11314320000132</t>
+  </si>
+  <si>
+    <t>Psi11314@2026</t>
+  </si>
+  <si>
+    <t>28 - JP TAMEIRAO GREGORIO SERVICOS MEDICOS LTDA</t>
+  </si>
+  <si>
+    <t>55964841000100</t>
+  </si>
+  <si>
+    <t>Joao@2025</t>
+  </si>
+  <si>
+    <t>19 - GORDINHO CASTELO COMERCIO DE BEBIDAS LTDA</t>
+  </si>
+  <si>
+    <t>54780099000110</t>
+  </si>
+  <si>
+    <t>29 - N MELGACO SERVICOS MEDICOS LTDA</t>
+  </si>
+  <si>
+    <t>55954443000103</t>
+  </si>
+  <si>
+    <t>Nathalia@2025</t>
+  </si>
+  <si>
+    <t>30 - IMPETO LTDA</t>
+  </si>
+  <si>
+    <t>29554530000163</t>
+  </si>
+  <si>
+    <t>Im29554@2026</t>
+  </si>
+  <si>
+    <t>31 - RAQUEL ATHAYDE SERVICOS MEDICOS LTDA</t>
+  </si>
+  <si>
+    <t>56301185000129</t>
+  </si>
+  <si>
+    <t>Raquel@2025</t>
+  </si>
+  <si>
+    <t>32 - VS MEDICINA LTDA</t>
+  </si>
+  <si>
+    <t>56301848000105</t>
+  </si>
+  <si>
+    <t>Victor@2025</t>
+  </si>
+  <si>
+    <t>35 - KELEN FERNANDES FISIOTERAPIA LTDA</t>
+  </si>
+  <si>
+    <t>57495487000148</t>
+  </si>
+  <si>
+    <t>Kelen@2025</t>
+  </si>
+  <si>
+    <t>37 - JCR MEDICINA LTDA</t>
+  </si>
+  <si>
+    <t>57814208000161</t>
+  </si>
+  <si>
+    <t>Jc57814@2025</t>
+  </si>
+  <si>
+    <t>38 - FSA SERVICOS MEDICOS LTDA</t>
+  </si>
+  <si>
+    <t>55329232000180</t>
+  </si>
+  <si>
+    <t>Fs55329@2026</t>
+  </si>
+  <si>
+    <t>39 - MATHEUS EVANGELISTA SIQUEIRA SERVICOS MEDICOS LTDA</t>
+  </si>
+  <si>
+    <t>49703898000153</t>
+  </si>
+  <si>
+    <t>Matheus@2025</t>
+  </si>
+  <si>
+    <t>40 - IGOR AMARAL SERVICOS MEDICOS LTDA</t>
+  </si>
+  <si>
+    <t>53201608000140</t>
+  </si>
+  <si>
+    <t>Igor@2025</t>
+  </si>
+  <si>
+    <t>43 - GABRIELLA B SERVICO MEDICO LTDA</t>
+  </si>
+  <si>
+    <t>55769380000115</t>
+  </si>
+  <si>
+    <t>Gabriella@2025</t>
+  </si>
+  <si>
+    <t>44 - DMS MEDICINA LTDA</t>
+  </si>
+  <si>
+    <t>59168194000181</t>
+  </si>
+  <si>
+    <t>Dm59168@2026</t>
+  </si>
+  <si>
+    <t>45 - GUIMARAES MANGABA INVESTIMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>59120406000150</t>
+  </si>
+  <si>
+    <t>Guima59120@2026</t>
+  </si>
+  <si>
+    <t>47 - BRACA SOLUCOES EM EMAGRECIMENTO E TREINAMENTO FISICO LTDA</t>
+  </si>
+  <si>
+    <t>59394664000125</t>
+  </si>
+  <si>
+    <t>1vnilGsx</t>
+  </si>
+  <si>
+    <t>48 - NATALIA LOURENCO MESQUITA</t>
+  </si>
+  <si>
+    <t>48939079000147</t>
+  </si>
+  <si>
+    <t>NM48939@2026</t>
+  </si>
+  <si>
+    <t>49 - BRUNA PB SERVICOS EM FISIOTERAPIA LIMITADA</t>
+  </si>
+  <si>
+    <t>55989486000124</t>
+  </si>
+  <si>
+    <t>Bruna@2025</t>
+  </si>
+  <si>
+    <t>50 - ANA GABRIELA ANDRADE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>46052636000188</t>
+  </si>
+  <si>
+    <t>Ana46052@2026</t>
+  </si>
+  <si>
+    <t>51 - GABRIELA AMORIM DE CASTRO</t>
+  </si>
+  <si>
+    <t>42350638000100</t>
+  </si>
+  <si>
+    <t>Gab42350@2026</t>
+  </si>
+  <si>
+    <t>52 - ENFANT CLINICA PEDIATRICA LTDA</t>
+  </si>
+  <si>
+    <t>45838235000195</t>
+  </si>
+  <si>
+    <t>Enfant@2025</t>
+  </si>
+  <si>
+    <t>54 - SOLLON NATHAN FREITAS ALMEIDA SERVICOS MEDICOS LTDA</t>
+  </si>
+  <si>
+    <t>58435946000160</t>
+  </si>
+  <si>
+    <t>56 - DG PALESTRAS E SAUDE LTDA</t>
+  </si>
+  <si>
+    <t>60287845000131</t>
+  </si>
+  <si>
+    <t>Dg60287@2026</t>
+  </si>
+  <si>
+    <t>57 - BRAGA SERVICOS MEDICOS LTDA</t>
+  </si>
+  <si>
+    <t>48813080000120</t>
+  </si>
+  <si>
+    <t>Braga@2025</t>
+  </si>
+  <si>
+    <t>58 - MAIPO SERVICOS MEDICOS LTDA</t>
+  </si>
+  <si>
+    <t>61030387000113</t>
+  </si>
+  <si>
+    <t>Maipo@2025</t>
+  </si>
+  <si>
+    <t>59 - THAIS QUARESMA MEDICINA LTDA</t>
+  </si>
+  <si>
+    <t>61257595000150</t>
+  </si>
+  <si>
+    <t>Thais@2025</t>
+  </si>
+  <si>
+    <t>61 - GUILHERME DUTRA SAUDE LTDA</t>
+  </si>
+  <si>
+    <t>61869250000157</t>
+  </si>
+  <si>
+    <t>Guilherme@2025</t>
+  </si>
+  <si>
+    <t>62 - JOYCE RODRIGUES SERVICOS MEDICOS LTDA</t>
+  </si>
+  <si>
+    <t>62219409000150</t>
+  </si>
+  <si>
+    <t>Joyce@2025</t>
+  </si>
+  <si>
+    <t>63 - MACIEL SERVICO MEDICO LTDA</t>
+  </si>
+  <si>
+    <t>62350101000140</t>
+  </si>
+  <si>
+    <t>64 - LNAS SERVICOS MEDICOS LTDA</t>
+  </si>
+  <si>
+    <t>62412593000150</t>
+  </si>
+  <si>
+    <t>Livia@2025</t>
+  </si>
+  <si>
+    <t>65 - JULIA RAYANE FERREIRA SILVA LTDA</t>
+  </si>
+  <si>
+    <t>55571256000140</t>
+  </si>
+  <si>
+    <t>1234567@</t>
+  </si>
+  <si>
+    <t>66 - MARCELA SILVA NASCIMENTO</t>
+  </si>
+  <si>
+    <t>62781581000101</t>
+  </si>
+  <si>
+    <t>Marcela@2025</t>
+  </si>
+  <si>
+    <t>67 - N.X. SERVICOS MEDICOS LTDA.</t>
+  </si>
+  <si>
+    <t>63167240000103</t>
+  </si>
+  <si>
+    <t>Marina@2025</t>
+  </si>
+  <si>
+    <t>68 - INSTITUTO SYNAPSE LTDA</t>
+  </si>
+  <si>
+    <t>63155137000135</t>
+  </si>
+  <si>
+    <t>Synapse@2025</t>
+  </si>
+  <si>
+    <t>69 - FB SERVICOS VETERINARIOS LTDA.</t>
+  </si>
+  <si>
+    <t>63289874000120</t>
+  </si>
+  <si>
+    <t>Fernanda@2025</t>
+  </si>
+  <si>
+    <t>70 - LLN SERVICOS ADMINISTRATIVOS E TREINAMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>63391724000123</t>
+  </si>
+  <si>
+    <t>Lln@2025</t>
+  </si>
+  <si>
+    <t>71 - ONSTAGE SOLUÇÕES FINANCEIRAS LTDA</t>
+  </si>
+  <si>
+    <t>48744243000160</t>
+  </si>
+  <si>
+    <t>Onstage@2026</t>
+  </si>
+  <si>
+    <t>73 - NJ RESENDE SERVICOS MEDICOS LTDA</t>
+  </si>
+  <si>
+    <t>53364064000138</t>
+  </si>
+  <si>
+    <t>NjMed@2025</t>
+  </si>
+  <si>
+    <t>74 - DB AVIATION LTDA</t>
+  </si>
+  <si>
+    <t>63415967000154</t>
+  </si>
+  <si>
+    <t>Diego@2025</t>
+  </si>
+  <si>
+    <t>75 - GRC MEDICINA LTDA</t>
+  </si>
+  <si>
+    <t>63597425000140</t>
+  </si>
+  <si>
+    <t>Gr63597@2025</t>
+  </si>
+  <si>
+    <t>76 - RAQUIMA SERVICOS MEDICOS LTDA</t>
+  </si>
+  <si>
+    <t>63747193000169</t>
+  </si>
+  <si>
+    <t>Ra63747@2025</t>
+  </si>
+  <si>
+    <t>77 - BENESSERE SERVICOS MEDICOS LTDA.</t>
+  </si>
+  <si>
+    <t>63777158000192</t>
+  </si>
+  <si>
+    <t>Be63777@2025</t>
+  </si>
+  <si>
+    <t>78 - CARDIOVET SERVICOS VETERINARIOS LTDA</t>
+  </si>
+  <si>
+    <t>63820094000165</t>
+  </si>
+  <si>
+    <t>79 - MJCJR SERVICOS MEDICOS LTDA</t>
+  </si>
+  <si>
+    <t>63838084000157</t>
+  </si>
+  <si>
+    <t>Ab63838@2025</t>
+  </si>
+  <si>
+    <t>81 - ALTOMARE OFTALMOLOGIA VETERINARIA LTDA</t>
+  </si>
+  <si>
+    <t>63920962000189</t>
+  </si>
+  <si>
+    <t>Al63920@2026</t>
+  </si>
+  <si>
+    <t>82 - ALF SERVICOS MEDICOS LTDA</t>
+  </si>
+  <si>
+    <t>64071221000133</t>
+  </si>
+  <si>
+    <t>Al64071@2026</t>
+  </si>
+  <si>
+    <t>83 - VSENRA SERVICOS MEDICOS LTDA</t>
+  </si>
+  <si>
+    <t>64160854000118</t>
+  </si>
+  <si>
+    <t>Se64160@2026</t>
+  </si>
+  <si>
+    <t>84 - MV. MATHEUS ANTONIO SERVICOS VETERINARIOS LTDA</t>
+  </si>
+  <si>
+    <t>64161062000168</t>
+  </si>
+  <si>
+    <t>Ma64161@2025</t>
+  </si>
+  <si>
+    <t>85 - MQ SERVICOS MEDICOS VETERINARIOS LTDA</t>
+  </si>
+  <si>
+    <t>64161199000112</t>
+  </si>
+  <si>
+    <t>So64161@2026</t>
+  </si>
+  <si>
+    <t>86 - LG VET SERVICOS MEDICOS VETERINARIOS LTDA</t>
+  </si>
+  <si>
+    <t>64166285000118</t>
+  </si>
+  <si>
+    <t>Lg64166@2026</t>
+  </si>
+  <si>
+    <t>87 - TOITIO SERVICOS MEDICOS LTDA</t>
+  </si>
+  <si>
+    <t>64126604000161</t>
+  </si>
+  <si>
+    <t>Gabriela2026</t>
+  </si>
+  <si>
+    <t>88 - AJPS SERVICOS MEDICOS LTDA</t>
+  </si>
+  <si>
+    <t>64302917000123</t>
+  </si>
+  <si>
+    <t>Al64302@2026</t>
+  </si>
+  <si>
+    <t>89 - JULIA PRADO POUZAS SERVICOS MEDICOS LTDA</t>
+  </si>
+  <si>
+    <t>64336739000151</t>
+  </si>
+  <si>
+    <t>Pr64336@2026</t>
+  </si>
+  <si>
+    <t>90 - JVO SERVICOS MEDICOS LTDA.</t>
+  </si>
+  <si>
+    <t>64352827000147</t>
+  </si>
+  <si>
+    <t>Jo64352@2026</t>
+  </si>
+  <si>
+    <t>91 - GONCALOS GUIMARAES SERVICOS MEDICOS LTDA</t>
+  </si>
+  <si>
+    <t>64358418000158</t>
+  </si>
+  <si>
+    <t>IG64358@2026</t>
+  </si>
+  <si>
+    <t>92 - MLJ SERVICOS MEDICOS LTDA</t>
+  </si>
+  <si>
+    <t>64380278000114</t>
+  </si>
+  <si>
+    <t>Ml64380@2026</t>
+  </si>
+  <si>
+    <t>93 - AJT SERVICOS MEDICOS LTDA</t>
+  </si>
+  <si>
+    <t>64417135000130</t>
+  </si>
+  <si>
+    <t>Aj64417@2026</t>
+  </si>
+  <si>
+    <t>94 - AHOC SERVICOS MEDICOS LTDA</t>
+  </si>
+  <si>
+    <t>64613401000108</t>
+  </si>
+  <si>
+    <t>Ah64613@2026</t>
+  </si>
+  <si>
+    <t>95 - RAFAELLA OLIVEIRA NEUROLOGIA VETERINARIA LTDA</t>
+  </si>
+  <si>
+    <t>24898695000139</t>
+  </si>
+  <si>
+    <t>Ra24898@2026</t>
+  </si>
+  <si>
+    <t>96 - IVK PRESTACAO DE SERVICOS MEDICOS LTDA</t>
+  </si>
+  <si>
+    <t>56703029000194</t>
+  </si>
+  <si>
+    <t>JHZ3duue</t>
+  </si>
+  <si>
+    <t>97 - 50.666.021 MILENA MARIA FERREIRA DE PAULA</t>
+  </si>
+  <si>
+    <t>50666021000119</t>
+  </si>
+  <si>
+    <t>Mi50666@2026</t>
+  </si>
+  <si>
+    <t>98 - BRUNO VALADARES PEREIRA SERVICOS MEDICOS LTDA</t>
+  </si>
+  <si>
+    <t>57431668000100</t>
+  </si>
+  <si>
+    <t>Br57431@2026</t>
+  </si>
+  <si>
+    <t>99 - LARISSA SANTIAGO GASTROENTEROLOGIA E HEPATOLOGIA VETERINARIA LTDA</t>
+  </si>
+  <si>
+    <t>64944773000109</t>
+  </si>
+  <si>
+    <t>La64944@2026</t>
+  </si>
+  <si>
+    <t>100 - ISABELLA OLIVEIRA RODARTE SERVICOS MEDICOS LTDA</t>
+  </si>
+  <si>
+    <t>61487677000190</t>
+  </si>
+  <si>
+    <t>101 - ALMEIDA &amp; SANTOS SERVICOS DE PRESTACOES HOSPITALARES LTDA</t>
+  </si>
+  <si>
+    <t>61939964000194</t>
+  </si>
+  <si>
+    <t>ma32548017</t>
+  </si>
+  <si>
+    <t>102 - DERMAPET AC VETERINARIA LTDA</t>
+  </si>
+  <si>
+    <t>65018703000192</t>
+  </si>
+  <si>
+    <t>De65018@2026</t>
+  </si>
+  <si>
+    <t>103 - M. LOPES SERVICOS MEDICOS LTDA</t>
+  </si>
+  <si>
+    <t>65088161000124</t>
+  </si>
+  <si>
+    <t>Medicina07!</t>
+  </si>
+  <si>
+    <t>104 - GASPAR SERVICOS MEDICOS LTDA</t>
+  </si>
+  <si>
+    <t>65736857000110</t>
+  </si>
+  <si>
+    <t>Ga65736@2026</t>
+  </si>
+  <si>
+    <t>105 - RIBEIRO NUNES SERVICOS MEDICOS LTDA.</t>
+  </si>
+  <si>
+    <t>65859239000167</t>
+  </si>
+  <si>
+    <t>Rib65859@2026</t>
+  </si>
+  <si>
+    <t>106 - DH SERVICOS MEDICOS LTDA</t>
+  </si>
+  <si>
+    <t>65866405000152</t>
+  </si>
+  <si>
+    <t>Si65866@2026</t>
   </si>
 </sst>
 </file>
@@ -380,7 +1100,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D84"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -411,6 +1131,1154 @@
         <v>0</v>
       </c>
     </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3">
+        <v>49456081</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" t="s">
+        <v>35</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" t="s">
+        <v>38</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>48</v>
+      </c>
+      <c r="B17" t="s">
+        <v>49</v>
+      </c>
+      <c r="C17">
+        <v>123456</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>50</v>
+      </c>
+      <c r="B18" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18" t="s">
+        <v>52</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>53</v>
+      </c>
+      <c r="B19" t="s">
+        <v>54</v>
+      </c>
+      <c r="C19" t="s">
+        <v>55</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>56</v>
+      </c>
+      <c r="B20" t="s">
+        <v>57</v>
+      </c>
+      <c r="C20" t="s">
+        <v>58</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>59</v>
+      </c>
+      <c r="B21" t="s">
+        <v>60</v>
+      </c>
+      <c r="C21" t="s">
+        <v>61</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>62</v>
+      </c>
+      <c r="B22" t="s">
+        <v>63</v>
+      </c>
+      <c r="C22" t="s">
+        <v>64</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>65</v>
+      </c>
+      <c r="B23" t="s">
+        <v>66</v>
+      </c>
+      <c r="C23" t="s">
+        <v>67</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>68</v>
+      </c>
+      <c r="B24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C24" t="s">
+        <v>70</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>71</v>
+      </c>
+      <c r="B25" t="s">
+        <v>72</v>
+      </c>
+      <c r="C25" t="s">
+        <v>73</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>74</v>
+      </c>
+      <c r="B26" t="s">
+        <v>75</v>
+      </c>
+      <c r="C26" t="s">
+        <v>76</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>77</v>
+      </c>
+      <c r="B27" t="s">
+        <v>78</v>
+      </c>
+      <c r="C27" t="s">
+        <v>79</v>
+      </c>
+      <c r="D27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>80</v>
+      </c>
+      <c r="B28" t="s">
+        <v>81</v>
+      </c>
+      <c r="C28" t="s">
+        <v>82</v>
+      </c>
+      <c r="D28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>83</v>
+      </c>
+      <c r="B29" t="s">
+        <v>84</v>
+      </c>
+      <c r="C29" t="s">
+        <v>85</v>
+      </c>
+      <c r="D29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>86</v>
+      </c>
+      <c r="B30" t="s">
+        <v>87</v>
+      </c>
+      <c r="C30" t="s">
+        <v>88</v>
+      </c>
+      <c r="D30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>89</v>
+      </c>
+      <c r="B31" t="s">
+        <v>90</v>
+      </c>
+      <c r="C31" t="s">
+        <v>91</v>
+      </c>
+      <c r="D31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>92</v>
+      </c>
+      <c r="B32" t="s">
+        <v>93</v>
+      </c>
+      <c r="C32" t="s">
+        <v>94</v>
+      </c>
+      <c r="D32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>95</v>
+      </c>
+      <c r="B33" t="s">
+        <v>96</v>
+      </c>
+      <c r="C33" t="s">
+        <v>97</v>
+      </c>
+      <c r="D33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>98</v>
+      </c>
+      <c r="B34" t="s">
+        <v>99</v>
+      </c>
+      <c r="C34" t="s">
+        <v>100</v>
+      </c>
+      <c r="D34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>101</v>
+      </c>
+      <c r="B35" t="s">
+        <v>102</v>
+      </c>
+      <c r="C35" t="s">
+        <v>103</v>
+      </c>
+      <c r="D35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>104</v>
+      </c>
+      <c r="B36" t="s">
+        <v>105</v>
+      </c>
+      <c r="C36">
+        <v>49456081</v>
+      </c>
+      <c r="D36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>106</v>
+      </c>
+      <c r="B37" t="s">
+        <v>107</v>
+      </c>
+      <c r="C37" t="s">
+        <v>108</v>
+      </c>
+      <c r="D37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>109</v>
+      </c>
+      <c r="B38" t="s">
+        <v>110</v>
+      </c>
+      <c r="C38" t="s">
+        <v>111</v>
+      </c>
+      <c r="D38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>112</v>
+      </c>
+      <c r="B39" t="s">
+        <v>113</v>
+      </c>
+      <c r="C39" t="s">
+        <v>114</v>
+      </c>
+      <c r="D39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>115</v>
+      </c>
+      <c r="B40" t="s">
+        <v>116</v>
+      </c>
+      <c r="C40" t="s">
+        <v>117</v>
+      </c>
+      <c r="D40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>118</v>
+      </c>
+      <c r="B41" t="s">
+        <v>119</v>
+      </c>
+      <c r="C41" t="s">
+        <v>120</v>
+      </c>
+      <c r="D41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>121</v>
+      </c>
+      <c r="B42" t="s">
+        <v>122</v>
+      </c>
+      <c r="C42" t="s">
+        <v>123</v>
+      </c>
+      <c r="D42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>124</v>
+      </c>
+      <c r="B43" t="s">
+        <v>125</v>
+      </c>
+      <c r="C43" t="s">
+        <v>41</v>
+      </c>
+      <c r="D43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>126</v>
+      </c>
+      <c r="B44" t="s">
+        <v>127</v>
+      </c>
+      <c r="C44" t="s">
+        <v>128</v>
+      </c>
+      <c r="D44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>129</v>
+      </c>
+      <c r="B45" t="s">
+        <v>130</v>
+      </c>
+      <c r="C45" t="s">
+        <v>131</v>
+      </c>
+      <c r="D45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>132</v>
+      </c>
+      <c r="B46" t="s">
+        <v>133</v>
+      </c>
+      <c r="C46" t="s">
+        <v>134</v>
+      </c>
+      <c r="D46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>135</v>
+      </c>
+      <c r="B47" t="s">
+        <v>136</v>
+      </c>
+      <c r="C47" t="s">
+        <v>137</v>
+      </c>
+      <c r="D47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>138</v>
+      </c>
+      <c r="B48" t="s">
+        <v>139</v>
+      </c>
+      <c r="C48" t="s">
+        <v>140</v>
+      </c>
+      <c r="D48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>141</v>
+      </c>
+      <c r="B49" t="s">
+        <v>142</v>
+      </c>
+      <c r="C49" t="s">
+        <v>143</v>
+      </c>
+      <c r="D49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>144</v>
+      </c>
+      <c r="B50" t="s">
+        <v>145</v>
+      </c>
+      <c r="C50" t="s">
+        <v>146</v>
+      </c>
+      <c r="D50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>147</v>
+      </c>
+      <c r="B51" t="s">
+        <v>148</v>
+      </c>
+      <c r="C51" t="s">
+        <v>149</v>
+      </c>
+      <c r="D51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>150</v>
+      </c>
+      <c r="B52" t="s">
+        <v>151</v>
+      </c>
+      <c r="C52" t="s">
+        <v>152</v>
+      </c>
+      <c r="D52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>153</v>
+      </c>
+      <c r="B53" t="s">
+        <v>154</v>
+      </c>
+      <c r="C53" t="s">
+        <v>155</v>
+      </c>
+      <c r="D53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>156</v>
+      </c>
+      <c r="B54" t="s">
+        <v>157</v>
+      </c>
+      <c r="C54" t="s">
+        <v>158</v>
+      </c>
+      <c r="D54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>159</v>
+      </c>
+      <c r="B55" t="s">
+        <v>160</v>
+      </c>
+      <c r="C55" t="s">
+        <v>161</v>
+      </c>
+      <c r="D55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>162</v>
+      </c>
+      <c r="B56" t="s">
+        <v>163</v>
+      </c>
+      <c r="C56" t="s">
+        <v>164</v>
+      </c>
+      <c r="D56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>165</v>
+      </c>
+      <c r="B57" t="s">
+        <v>166</v>
+      </c>
+      <c r="C57" t="s">
+        <v>164</v>
+      </c>
+      <c r="D57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>167</v>
+      </c>
+      <c r="B58" t="s">
+        <v>168</v>
+      </c>
+      <c r="C58" t="s">
+        <v>169</v>
+      </c>
+      <c r="D58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>170</v>
+      </c>
+      <c r="B59" t="s">
+        <v>171</v>
+      </c>
+      <c r="C59" t="s">
+        <v>172</v>
+      </c>
+      <c r="D59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>173</v>
+      </c>
+      <c r="B60" t="s">
+        <v>174</v>
+      </c>
+      <c r="C60" t="s">
+        <v>175</v>
+      </c>
+      <c r="D60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>176</v>
+      </c>
+      <c r="B61" t="s">
+        <v>177</v>
+      </c>
+      <c r="C61" t="s">
+        <v>178</v>
+      </c>
+      <c r="D61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>179</v>
+      </c>
+      <c r="B62" t="s">
+        <v>180</v>
+      </c>
+      <c r="C62" t="s">
+        <v>181</v>
+      </c>
+      <c r="D62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>182</v>
+      </c>
+      <c r="B63" t="s">
+        <v>183</v>
+      </c>
+      <c r="C63" t="s">
+        <v>184</v>
+      </c>
+      <c r="D63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>185</v>
+      </c>
+      <c r="B64" t="s">
+        <v>186</v>
+      </c>
+      <c r="C64" t="s">
+        <v>187</v>
+      </c>
+      <c r="D64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>188</v>
+      </c>
+      <c r="B65" t="s">
+        <v>189</v>
+      </c>
+      <c r="C65" t="s">
+        <v>190</v>
+      </c>
+      <c r="D65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>191</v>
+      </c>
+      <c r="B66" t="s">
+        <v>192</v>
+      </c>
+      <c r="C66" t="s">
+        <v>193</v>
+      </c>
+      <c r="D66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>194</v>
+      </c>
+      <c r="B67" t="s">
+        <v>195</v>
+      </c>
+      <c r="C67" t="s">
+        <v>196</v>
+      </c>
+      <c r="D67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>197</v>
+      </c>
+      <c r="B68" t="s">
+        <v>198</v>
+      </c>
+      <c r="C68" t="s">
+        <v>199</v>
+      </c>
+      <c r="D68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>200</v>
+      </c>
+      <c r="B69" t="s">
+        <v>201</v>
+      </c>
+      <c r="C69" t="s">
+        <v>202</v>
+      </c>
+      <c r="D69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>203</v>
+      </c>
+      <c r="B70" t="s">
+        <v>204</v>
+      </c>
+      <c r="C70" t="s">
+        <v>205</v>
+      </c>
+      <c r="D70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>206</v>
+      </c>
+      <c r="B71" t="s">
+        <v>207</v>
+      </c>
+      <c r="C71" t="s">
+        <v>208</v>
+      </c>
+      <c r="D71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>209</v>
+      </c>
+      <c r="B72" t="s">
+        <v>210</v>
+      </c>
+      <c r="C72" t="s">
+        <v>211</v>
+      </c>
+      <c r="D72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>212</v>
+      </c>
+      <c r="B73" t="s">
+        <v>213</v>
+      </c>
+      <c r="C73" t="s">
+        <v>214</v>
+      </c>
+      <c r="D73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>215</v>
+      </c>
+      <c r="B74" t="s">
+        <v>216</v>
+      </c>
+      <c r="C74" t="s">
+        <v>217</v>
+      </c>
+      <c r="D74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>218</v>
+      </c>
+      <c r="B75" t="s">
+        <v>219</v>
+      </c>
+      <c r="C75" t="s">
+        <v>220</v>
+      </c>
+      <c r="D75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>221</v>
+      </c>
+      <c r="B76" t="s">
+        <v>222</v>
+      </c>
+      <c r="C76" t="s">
+        <v>223</v>
+      </c>
+      <c r="D76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>224</v>
+      </c>
+      <c r="B77" t="s">
+        <v>225</v>
+      </c>
+      <c r="C77" t="s">
+        <v>226</v>
+      </c>
+      <c r="D77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>227</v>
+      </c>
+      <c r="B78" t="s">
+        <v>228</v>
+      </c>
+      <c r="C78">
+        <v>1234</v>
+      </c>
+      <c r="D78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>229</v>
+      </c>
+      <c r="B79" t="s">
+        <v>230</v>
+      </c>
+      <c r="C79" t="s">
+        <v>231</v>
+      </c>
+      <c r="D79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>232</v>
+      </c>
+      <c r="B80" t="s">
+        <v>233</v>
+      </c>
+      <c r="C80" t="s">
+        <v>234</v>
+      </c>
+      <c r="D80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>235</v>
+      </c>
+      <c r="B81" t="s">
+        <v>236</v>
+      </c>
+      <c r="C81" t="s">
+        <v>237</v>
+      </c>
+      <c r="D81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>238</v>
+      </c>
+      <c r="B82" t="s">
+        <v>239</v>
+      </c>
+      <c r="C82" t="s">
+        <v>240</v>
+      </c>
+      <c r="D82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>241</v>
+      </c>
+      <c r="B83" t="s">
+        <v>242</v>
+      </c>
+      <c r="C83" t="s">
+        <v>243</v>
+      </c>
+      <c r="D83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>244</v>
+      </c>
+      <c r="B84" t="s">
+        <v>245</v>
+      </c>
+      <c r="C84" t="s">
+        <v>246</v>
+      </c>
+      <c r="D84">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/empresas_backup.xlsx
+++ b/empresas_backup.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tiago\OneDrive\Documentos\Python\onstage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tiago\OneDrive\Documentos\Python\AccSim Analytics\onstage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{738A57FA-B265-40D2-ACD1-E747E6317E17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A4BF0D9-4C7D-4F78-B8E7-A06995744497}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1101,9 +1101,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D84"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1117,7 +1117,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1131,7 +1131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1145,7 +1145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -1159,7 +1159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -1187,7 +1187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -1201,7 +1201,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -1215,7 +1215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -1229,7 +1229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>27</v>
       </c>
@@ -1243,7 +1243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -1257,7 +1257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -1271,7 +1271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>36</v>
       </c>
@@ -1285,7 +1285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>39</v>
       </c>
@@ -1299,7 +1299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -1313,7 +1313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>45</v>
       </c>
@@ -1327,7 +1327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>48</v>
       </c>
@@ -1341,7 +1341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>50</v>
       </c>
@@ -1355,7 +1355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>53</v>
       </c>
@@ -1369,7 +1369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>56</v>
       </c>
@@ -1383,7 +1383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>59</v>
       </c>
@@ -1397,7 +1397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>62</v>
       </c>
@@ -1411,7 +1411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>65</v>
       </c>
@@ -1425,7 +1425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>68</v>
       </c>
@@ -1439,7 +1439,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>71</v>
       </c>
@@ -1453,7 +1453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>74</v>
       </c>
@@ -1467,7 +1467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>77</v>
       </c>
@@ -1481,7 +1481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>80</v>
       </c>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>83</v>
       </c>
@@ -1509,7 +1509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>86</v>
       </c>
@@ -1523,7 +1523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>89</v>
       </c>
@@ -1537,7 +1537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>92</v>
       </c>
@@ -1551,7 +1551,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>95</v>
       </c>
@@ -1565,7 +1565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>98</v>
       </c>
@@ -1579,7 +1579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>101</v>
       </c>
@@ -1593,7 +1593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>104</v>
       </c>
@@ -1607,7 +1607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>106</v>
       </c>
@@ -1621,7 +1621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>109</v>
       </c>
@@ -1635,7 +1635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>112</v>
       </c>
@@ -1649,7 +1649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>115</v>
       </c>
@@ -1663,7 +1663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>118</v>
       </c>
@@ -1677,7 +1677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>121</v>
       </c>
@@ -1691,7 +1691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>124</v>
       </c>
@@ -1705,7 +1705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>126</v>
       </c>
@@ -1719,7 +1719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>129</v>
       </c>
@@ -1733,7 +1733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>132</v>
       </c>
@@ -1747,7 +1747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>135</v>
       </c>
@@ -1761,7 +1761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>138</v>
       </c>
@@ -1775,7 +1775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>141</v>
       </c>
@@ -1789,7 +1789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>144</v>
       </c>
@@ -1803,7 +1803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>147</v>
       </c>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>150</v>
       </c>
@@ -1831,7 +1831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>153</v>
       </c>
@@ -1845,7 +1845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>156</v>
       </c>
@@ -1859,7 +1859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>159</v>
       </c>
@@ -1873,7 +1873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>162</v>
       </c>
@@ -1887,7 +1887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>165</v>
       </c>
@@ -1901,7 +1901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>167</v>
       </c>
@@ -1915,7 +1915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>170</v>
       </c>
@@ -1929,7 +1929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>173</v>
       </c>
@@ -1943,7 +1943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>176</v>
       </c>
@@ -1957,7 +1957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>179</v>
       </c>
@@ -1971,7 +1971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>182</v>
       </c>
@@ -1985,7 +1985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>185</v>
       </c>
@@ -1999,7 +1999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>188</v>
       </c>
@@ -2013,7 +2013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>191</v>
       </c>
@@ -2027,7 +2027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>194</v>
       </c>
@@ -2041,7 +2041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>197</v>
       </c>
@@ -2055,7 +2055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>200</v>
       </c>
@@ -2069,7 +2069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>203</v>
       </c>
@@ -2083,7 +2083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>206</v>
       </c>
@@ -2097,7 +2097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>209</v>
       </c>
@@ -2111,7 +2111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>212</v>
       </c>
@@ -2125,7 +2125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>215</v>
       </c>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>218</v>
       </c>
@@ -2153,7 +2153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>221</v>
       </c>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>224</v>
       </c>
@@ -2181,7 +2181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>227</v>
       </c>
@@ -2195,7 +2195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>229</v>
       </c>
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>232</v>
       </c>
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>235</v>
       </c>
@@ -2237,7 +2237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>238</v>
       </c>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>241</v>
       </c>
@@ -2265,7 +2265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>244</v>
       </c>

--- a/empresas_backup.xlsx
+++ b/empresas_backup.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tiago\OneDrive\Documentos\Python\AccSim Analytics\onstage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A4BF0D9-4C7D-4F78-B8E7-A06995744497}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB2853E4-6161-4EF0-9820-ABF5583AE0C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="249">
   <si>
     <t>Nome empresa</t>
   </si>
@@ -166,12 +166,6 @@
     <t>Joao@2025</t>
   </si>
   <si>
-    <t>19 - GORDINHO CASTELO COMERCIO DE BEBIDAS LTDA</t>
-  </si>
-  <si>
-    <t>54780099000110</t>
-  </si>
-  <si>
     <t>29 - N MELGACO SERVICOS MEDICOS LTDA</t>
   </si>
   <si>
@@ -286,7 +280,7 @@
     <t>59394664000125</t>
   </si>
   <si>
-    <t>1vnilGsx</t>
+    <t>Br59394@2026</t>
   </si>
   <si>
     <t>48 - NATALIA LOURENCO MESQUITA</t>
@@ -340,6 +334,9 @@
     <t>58435946000160</t>
   </si>
   <si>
+    <t>So58435@2025</t>
+  </si>
+  <si>
     <t>56 - DG PALESTRAS E SAUDE LTDA</t>
   </si>
   <si>
@@ -364,7 +361,7 @@
     <t>61030387000113</t>
   </si>
   <si>
-    <t>Maipo@2025</t>
+    <t>Ma61030@2026</t>
   </si>
   <si>
     <t>59 - THAIS QUARESMA MEDICINA LTDA</t>
@@ -415,7 +412,7 @@
     <t>55571256000140</t>
   </si>
   <si>
-    <t>1234567@</t>
+    <t>Jf5557@2026</t>
   </si>
   <si>
     <t>66 - MARCELA SILVA NASCIMENTO</t>
@@ -445,15 +442,6 @@
     <t>Synapse@2025</t>
   </si>
   <si>
-    <t>69 - FB SERVICOS VETERINARIOS LTDA.</t>
-  </si>
-  <si>
-    <t>63289874000120</t>
-  </si>
-  <si>
-    <t>Fernanda@2025</t>
-  </si>
-  <si>
     <t>70 - LLN SERVICOS ADMINISTRATIVOS E TREINAMENTOS LTDA</t>
   </si>
   <si>
@@ -679,9 +667,6 @@
     <t>97 - 50.666.021 MILENA MARIA FERREIRA DE PAULA</t>
   </si>
   <si>
-    <t>50666021000119</t>
-  </si>
-  <si>
     <t>Mi50666@2026</t>
   </si>
   <si>
@@ -761,6 +746,27 @@
   </si>
   <si>
     <t>Si65866@2026</t>
+  </si>
+  <si>
+    <t>107 - MSRAMOS SERVICOS MEDICOS LTDA.</t>
+  </si>
+  <si>
+    <t>66041123000189</t>
+  </si>
+  <si>
+    <t>Ms66041@2026</t>
+  </si>
+  <si>
+    <t>108 - CLINICA SENA SERVICOS MEDICOS LTDA</t>
+  </si>
+  <si>
+    <t>66505360000153</t>
+  </si>
+  <si>
+    <t>Cli66505@2026</t>
+  </si>
+  <si>
+    <t>66332070000155</t>
   </si>
 </sst>
 </file>
@@ -796,8 +802,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1102,6 +1109,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D84"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="72.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -1128,7 +1141,7 @@
         <v>6</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>160</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -1142,7 +1155,7 @@
         <v>49456081</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -1156,7 +1169,7 @@
         <v>11</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>309</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -1170,7 +1183,7 @@
         <v>14</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -1184,7 +1197,7 @@
         <v>17</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -1198,7 +1211,7 @@
         <v>20</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -1212,7 +1225,7 @@
         <v>23</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -1226,7 +1239,7 @@
         <v>26</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
@@ -1240,7 +1253,7 @@
         <v>29</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -1254,7 +1267,7 @@
         <v>32</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
@@ -1268,7 +1281,7 @@
         <v>35</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
@@ -1282,7 +1295,7 @@
         <v>38</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
@@ -1296,7 +1309,7 @@
         <v>41</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
@@ -1310,7 +1323,7 @@
         <v>44</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>270</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
@@ -1324,7 +1337,7 @@
         <v>47</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>81</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
@@ -1334,806 +1347,806 @@
       <c r="B17" t="s">
         <v>49</v>
       </c>
-      <c r="C17">
-        <v>123456</v>
+      <c r="C17" t="s">
+        <v>50</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B18" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C18" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>1753</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B19" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B20" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>117</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B21" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C21" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>219</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B22" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C22" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>218</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B23" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C23" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>69</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B24" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C24" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B25" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C25" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B26" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C26" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>31</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B27" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C27" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>31</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B28" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C28" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B29" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C29" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>204</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B30" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C30" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B31" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C31" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B32" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C32" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B33" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C33" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B34" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C34" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D34">
-        <v>0</v>
+        <v>403</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B35" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C35" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>398</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B36" t="s">
-        <v>105</v>
-      </c>
-      <c r="C36">
-        <v>49456081</v>
+        <v>106</v>
+      </c>
+      <c r="C36" t="s">
+        <v>107</v>
       </c>
       <c r="D36">
-        <v>0</v>
+        <v>65</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B37" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C37" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B38" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C38" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>147</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B39" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C39" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>56</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B40" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C40" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D40">
-        <v>0</v>
+        <v>55</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B41" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C41" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>31</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B42" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C42" t="s">
-        <v>123</v>
+        <v>41</v>
       </c>
       <c r="D42">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B43" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C43" t="s">
-        <v>41</v>
+        <v>127</v>
       </c>
       <c r="D43">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B44" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C44" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D44">
-        <v>0</v>
+        <v>46</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B45" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C45" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D45">
-        <v>0</v>
+        <v>45</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B46" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C46" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D46">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B47" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C47" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D47">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B48" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C48" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D48">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B49" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C49" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D49">
-        <v>0</v>
+        <v>818</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B50" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C50" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D50">
-        <v>0</v>
+        <v>81</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B51" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C51" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D51">
-        <v>0</v>
+        <v>784</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B52" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C52" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D52">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B53" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C53" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D53">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B54" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C54" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D54">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B55" t="s">
+        <v>162</v>
+      </c>
+      <c r="C55" t="s">
         <v>160</v>
       </c>
-      <c r="C55" t="s">
-        <v>161</v>
-      </c>
       <c r="D55">
-        <v>0</v>
+        <v>167</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B56" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C56" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D56">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B57" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C57" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="D57">
-        <v>0</v>
+        <v>152</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B58" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C58" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D58">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B59" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C59" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D59">
-        <v>0</v>
+        <v>51</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B60" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C60" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D60">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B61" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C61" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D61">
-        <v>0</v>
+        <v>37</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B62" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C62" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D62">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B63" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C63" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D63">
-        <v>0</v>
+        <v>37</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B64" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C64" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D64">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B65" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C65" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D65">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B66" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C66" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D66">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B67" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C67" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D67">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B68" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C68" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D68">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B69" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C69" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D69">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B70" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C70" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D70">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B71" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C71" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D71">
-        <v>0</v>
+        <v>202</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B72" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C72" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D72">
-        <v>0</v>
+        <v>39</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>212</v>
-      </c>
-      <c r="B73" t="s">
-        <v>213</v>
+        <v>214</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>248</v>
       </c>
       <c r="C73" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D73">
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B74" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C74" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D74">
         <v>0</v>
@@ -2141,30 +2154,30 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B75" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C75" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D75">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B76" t="s">
-        <v>222</v>
-      </c>
-      <c r="C76" t="s">
         <v>223</v>
       </c>
+      <c r="C76">
+        <v>1234</v>
+      </c>
       <c r="D76">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
@@ -2178,7 +2191,7 @@
         <v>226</v>
       </c>
       <c r="D77">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
@@ -2188,95 +2201,95 @@
       <c r="B78" t="s">
         <v>228</v>
       </c>
-      <c r="C78">
-        <v>1234</v>
+      <c r="C78" t="s">
+        <v>229</v>
       </c>
       <c r="D78">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B79" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C79" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D79">
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B80" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C80" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D80">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B81" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C81" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D81">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B82" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C82" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D82">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B83" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C83" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D83">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B84" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C84" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D84">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
